--- a/erp-server/erp-server-wms/src/main/resources/excel/packingTaskExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/packingTaskExport.xlsx
@@ -64,7 +64,7 @@
     <t>发货仓库</t>
   </si>
   <si>
-    <t>创建任</t>
+    <t>创建人</t>
   </si>
   <si>
     <t>创建时间</t>
